--- a/V5.0_双人执行工作区/B_AI交付/03_AIChat配置/AI_RESOURCE_INVENTORY_V50.xlsx
+++ b/V5.0_双人执行工作区/B_AI交付/03_AIChat配置/AI_RESOURCE_INVENTORY_V50.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资源清单" sheetId="1" r:id="R6cd8705622ba46d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资源清单" sheetId="1" r:id="Rffff5331377e4cd6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -335,7 +335,7 @@
         <x:color rgb="FF8A5A00"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4D6"/>
         </x:patternFill>
       </x:fill>
@@ -345,7 +345,7 @@
         <x:color rgb="FFA12828"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDECEC"/>
         </x:patternFill>
       </x:fill>
@@ -581,7 +581,7 @@
     </x:row>
     <x:row r="2" ht="34" customHeight="1">
       <x:c r="A2" s="8" t="str">
-        <x:v>当前状态：CONFIG_ALLOWED / BUILD_PENDING / FORMAL_PASS_NOT_REACHED。G2 仅为启动放行，最终冻结修订号与平台实测证据待补。</x:v>
+        <x:v>当前状态：KB_CREATED / FILES_0 / INDEX_PENDING / CONFIG_NOT_EXECUTED / FORMAL_25Q_0_OF_25。空库已建，七类独立导入文件已准备。</x:v>
       </x:c>
       <x:c r="B2" s="8"/>
       <x:c r="C2" s="8"/>
@@ -718,21 +718,25 @@
         <x:v>A</x:v>
       </x:c>
       <x:c r="F7" s="21" t="str">
-        <x:v>MATERIAL_PARTIAL / NOT_UPLOADED</x:v>
+        <x:v>KB_CREATED / FILES_0 / INDEX_PENDING</x:v>
       </x:c>
       <x:c r="G7" s="21" t="str">
-        <x:v>七类 KB 清单见 KB_FILE_MANIFEST_V50.xlsx</x:v>
+        <x:v>2026-08-31空库创建；七类导入包以KB_FILE_MANIFEST当前版本为准</x:v>
       </x:c>
       <x:c r="H7" s="21" t="str">
-        <x:v>仅批准的七类材料</x:v>
+        <x:v>仅KB_UPLOAD_READY下七类独立文件</x:v>
       </x:c>
       <x:c r="I7" s="21" t="str">
-        <x:v>否</x:v>
-      </x:c>
-      <x:c r="J7" s="21" t="str"/>
-      <x:c r="K7" s="21" t="str"/>
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="J7" s="21" t="str">
+        <x:v>实机创建与空列表截图已确认；正式证据待归档</x:v>
+      </x:c>
+      <x:c r="K7" s="21" t="str">
+        <x:v>2026-08-31 14:11:55 +08:00</x:v>
+      </x:c>
       <x:c r="L7" s="21" t="str">
-        <x:v>第1/3/4类仍需按当前冻结与页面状态补齐</x:v>
+        <x:v>知识库对象已创建；当前0文件，尚未上传、索引或检索。</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="62" customHeight="1">

--- a/V5.0_双人执行工作区/B_AI交付/03_AIChat配置/AI_RESOURCE_INVENTORY_V50.xlsx
+++ b/V5.0_双人执行工作区/B_AI交付/03_AIChat配置/AI_RESOURCE_INVENTORY_V50.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资源清单" sheetId="1" r:id="Rffff5331377e4cd6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资源清单" sheetId="1" r:id="R5a86ffba32b7470c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -581,7 +581,7 @@
     </x:row>
     <x:row r="2" ht="34" customHeight="1">
       <x:c r="A2" s="8" t="str">
-        <x:v>当前状态：KB_CREATED / FILES_0 / INDEX_PENDING / CONFIG_NOT_EXECUTED / FORMAL_25Q_0_OF_25。空库已建，七类独立导入文件已准备。</x:v>
+        <x:v>当前状态：KB_CREATED / KNOWLEDGE_ROWS_0 / RETRIEVAL_PENDING / CONFIG_NOT_EXECUTED / FORMAL_25Q_0_OF_25。空库已建，七个维护源与模板CSV已准备。</x:v>
       </x:c>
       <x:c r="B2" s="8"/>
       <x:c r="C2" s="8"/>
@@ -718,25 +718,25 @@
         <x:v>A</x:v>
       </x:c>
       <x:c r="F7" s="21" t="str">
-        <x:v>KB_CREATED / FILES_0 / INDEX_PENDING</x:v>
+        <x:v>KB_CREATED / KNOWLEDGE_ROWS_0 / RETRIEVAL_PENDING</x:v>
       </x:c>
       <x:c r="G7" s="21" t="str">
-        <x:v>2026-08-31空库创建；七类导入包以KB_FILE_MANIFEST当前版本为准</x:v>
+        <x:v>2026-08-31空库创建；CSV导入包以KB_FILE_MANIFEST当前版本为准</x:v>
       </x:c>
       <x:c r="H7" s="21" t="str">
-        <x:v>仅KB_UPLOAD_READY下七类独立文件</x:v>
+        <x:v>仅导入KB_UPLOAD_READY/KB_XH202612_V50_GOVERNANCE_知识导入_V50.csv；7个MD为维护源</x:v>
       </x:c>
       <x:c r="I7" s="21" t="str">
         <x:v>是</x:v>
       </x:c>
       <x:c r="J7" s="21" t="str">
-        <x:v>实机创建与空列表截图已确认；正式证据待归档</x:v>
+        <x:v>实机创建与空知识列表截图已确认；CSV导入证据待归档</x:v>
       </x:c>
       <x:c r="K7" s="21" t="str">
         <x:v>2026-08-31 14:11:55 +08:00</x:v>
       </x:c>
       <x:c r="L7" s="21" t="str">
-        <x:v>知识库对象已创建；当前0文件，尚未上传、索引或检索。</x:v>
+        <x:v>知识库对象已创建；当前0条知识，尚未导入或检索。</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="62" customHeight="1">

--- a/V5.0_双人执行工作区/B_AI交付/03_AIChat配置/AI_RESOURCE_INVENTORY_V50.xlsx
+++ b/V5.0_双人执行工作区/B_AI交付/03_AIChat配置/AI_RESOURCE_INVENTORY_V50.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资源清单" sheetId="1" r:id="R5a86ffba32b7470c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资源清单" sheetId="1" r:id="R758941f78e95461b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -579,9 +579,9 @@
       <x:c r="K1" s="4"/>
       <x:c r="L1" s="4"/>
     </x:row>
-    <x:row r="2" ht="34" customHeight="1">
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="8" t="str">
-        <x:v>当前状态：KB_CREATED / KNOWLEDGE_ROWS_0 / RETRIEVAL_PENDING / CONFIG_NOT_EXECUTED / FORMAL_25Q_0_OF_25。空库已建，七个维护源与模板CSV已准备。</x:v>
+        <x:v>当前状态：KB_IMPORTED_43 / ALL_ENABLED / ROW_RESAVE_REINDEXED / RETRIEVAL_PASS_7_OF_7 / MODEL_GRAPH_BUILD_PASS / AIP_CREATED_MODEL_BOUND / AGENT_PUBLISHED / PROMPT_V50-B04-LOCAL_FINAL-r10 / SMOKE_5_OF_5 / AI04_PASS / AI06_PASS / AI22_PASS / AI17_PASS / AI18_PASS / FORMAL_25Q_25_OF_25 / B04_PASS_CANDIDATE_A_REVIEW_PENDING。AIP ID=I8a8083f701a055ad55adbe1301a0586978653e62；Agent ID=I8a8083f701a055ad55adbe1301a0588b11c03e73。</x:v>
       </x:c>
       <x:c r="B2" s="8"/>
       <x:c r="C2" s="8"/>
@@ -633,7 +633,7 @@
         <x:v>备注</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="62" customHeight="1">
+    <x:row r="5" ht="24" hidden="0" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>正式模型</x:v>
       </x:c>
@@ -653,7 +653,7 @@
         <x:v>G2_START_RELEASE / FINAL_FREEZE_PENDING</x:v>
       </x:c>
       <x:c r="G5" s="20" t="str">
-        <x:v>G2_START_RELEASE_20260828；MODEL_HANDOFF 仍为 V5.0-A04-DRAFT-r3</x:v>
+        <x:v>模型=MDL_XH202612_V50_COUNTRY_RESERVE；版本=MDL_XH202612_V50_COUNTRY_RESERVE/runtime-20260901；MODEL_GRAPH_BUILD_PASS</x:v>
       </x:c>
       <x:c r="H5" s="20" t="str">
         <x:v>无；该对象是上游绑定源</x:v>
@@ -661,13 +661,17 @@
       <x:c r="I5" s="20" t="str">
         <x:v>是（G2 记录）</x:v>
       </x:c>
-      <x:c r="J5" s="20" t="str"/>
-      <x:c r="K5" s="20" t="str"/>
+      <x:c r="J5" s="20" t="str">
+        <x:v>证据/B04_20260831/B04_14_固定模型图谱构建成功_20260831.png；证据/B04_20260831/B04_15_AIP固定模型绑定成功_20260831.png</x:v>
+      </x:c>
+      <x:c r="K5" s="20" t="n">
+        <x:v>46265.79597222222</x:v>
+      </x:c>
       <x:c r="L5" s="20" t="str">
         <x:v>不得由 B 修改；后续变更须登记影响范围并定向复测</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="62" customHeight="1">
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="25" t="str">
         <x:v>AI 项目（AIP）</x:v>
       </x:c>
@@ -684,24 +688,28 @@
         <x:v>A</x:v>
       </x:c>
       <x:c r="F6" s="21" t="str">
-        <x:v>NOT_CREATED</x:v>
+        <x:v>CREATED / MODEL_BOUND</x:v>
       </x:c>
       <x:c r="G6" s="21" t="str">
-        <x:v>待平台创建后填写</x:v>
+        <x:v>AIP ID=I8a8083f701a055ad55adbe1301a0586978653e62；绑定模型=MDL_XH202612_V50_COUNTRY_RESERVE；模型版本=MDL_XH202612_V50_COUNTRY_RESERVE/runtime-20260901</x:v>
       </x:c>
       <x:c r="H6" s="21" t="str">
-        <x:v>项目描述仅放本项目治理上下文</x:v>
+        <x:v>固定模型=MDL_XH202612_V50_COUNTRY_RESERVE；KB=KB_XH202612_V50_GOVERNANCE；AGENT=AGENT_XH202612_V50_ASSISTANT</x:v>
       </x:c>
       <x:c r="I6" s="21" t="str">
-        <x:v>否</x:v>
-      </x:c>
-      <x:c r="J6" s="21" t="str"/>
-      <x:c r="K6" s="21" t="str"/>
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="J6" s="21" t="str">
+        <x:v>证据/B04_20260831/B04_15_AIP固定模型绑定成功_20260831.png</x:v>
+      </x:c>
+      <x:c r="K6" s="21" t="n">
+        <x:v>46265.79597222222</x:v>
+      </x:c>
       <x:c r="L6" s="21" t="str">
-        <x:v>平台实际名称为“项目”；逻辑对象名按计划书固定</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="62" customHeight="1">
+        <x:v>平台对象已创建并绑定固定模型；资源ID=I8a8083f701a055ad55adbe1301a0586978653e62。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="48" hidden="0" customHeight="1">
       <x:c r="A7" s="25" t="str">
         <x:v>知识库（KB）</x:v>
       </x:c>
@@ -718,28 +726,28 @@
         <x:v>A</x:v>
       </x:c>
       <x:c r="F7" s="21" t="str">
-        <x:v>KB_CREATED / KNOWLEDGE_ROWS_0 / RETRIEVAL_PENDING</x:v>
+        <x:v>KNOWLEDGE_ROWS_43 / ALL_ENABLED / ROW_RESAVE_REINDEXED / RETRIEVAL_PASS_7_OF_7</x:v>
       </x:c>
       <x:c r="G7" s="21" t="str">
-        <x:v>2026-08-31空库创建；CSV导入包以KB_FILE_MANIFEST当前版本为准</x:v>
+        <x:v>ALL_IN_IMPORT_ORDER.csv；initial_import_sha256=5de78eea5d88f8d5d7cb3bfb3e0f3bc899e755c26ed58cc6834c8bcdfa29167c；current_synced_source_sha256=f9b98523b9c4f7d0c89e97cfd60ce4d14eb837209004a14c5b697dc09215b022；PLAIN / ENABLE / V1</x:v>
       </x:c>
       <x:c r="H7" s="21" t="str">
-        <x:v>仅导入KB_UPLOAD_READY/KB_XH202612_V50_GOVERNANCE_知识导入_V50.csv；7个MD为维护源</x:v>
+        <x:v>禁止重复导入或删除43条；检索7/7通过后允许绑定AIP/AGENT。</x:v>
       </x:c>
       <x:c r="I7" s="21" t="str">
         <x:v>是</x:v>
       </x:c>
       <x:c r="J7" s="21" t="str">
-        <x:v>实机创建与空知识列表截图已确认；CSV导入证据待归档</x:v>
-      </x:c>
-      <x:c r="K7" s="21" t="str">
-        <x:v>2026-08-31 14:11:55 +08:00</x:v>
+        <x:v>证据/B04_20260831/B04_01_KB43条全部启用_20260831.png；B04_02_完整标题阈值0_向量检索0命中_20260831.png；B04_05/06 唯一词检索0命中；证据/B04_20260831/B04_07_模型检索_PASS_20260831.png；证据/B04_20260831/B04_08_口径检索_PASS_20260831.png；证据/B04_20260831/B04_09_页面检索_PASS_20260831.png；证据/B04_20260831/B04_10_来源检索_PASS_20260831.png；证据/B04_20260831/B04_11_边界检索_PASS_20260831.png；证据/B04_20260831/B04_12_25问检索_PASS_20260831.png；证据/B04_20260831/B04_13_合规检索_PASS_20260831.png</x:v>
+      </x:c>
+      <x:c r="K7" s="21" t="n">
+        <x:v>46265.79597222222</x:v>
       </x:c>
       <x:c r="L7" s="21" t="str">
-        <x:v>知识库对象已创建；当前0条知识，尚未导入或检索。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="62" customHeight="1">
+        <x:v>43条逐行重新保存触发重索引；正式7类向量检索7/7 PASS。旧失败截图保留为恢复前过程证据。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="24" hidden="0" customHeight="1">
       <x:c r="A8" s="25" t="str">
         <x:v>智能体（AGENT）</x:v>
       </x:c>
@@ -756,24 +764,28 @@
         <x:v>A</x:v>
       </x:c>
       <x:c r="F8" s="21" t="str">
-        <x:v>NOT_CREATED</x:v>
+        <x:v>PUBLISHED / CONFIGURED</x:v>
       </x:c>
       <x:c r="G8" s="21" t="str">
-        <x:v>待平台创建后填写</x:v>
+        <x:v>Agent ID=I8a8083f701a055ad55adbe1301a0588b11c03e73；Prompt=V50-B04-LOCAL_FINAL-r10</x:v>
       </x:c>
       <x:c r="H8" s="21" t="str">
-        <x:v>开始 → 知识库检索 → 大模型 → 结束；不得写共享模型</x:v>
+        <x:v>开始 → 知识库检索 → 大模型 → 结束；模型=MDL_XH202612_V50_COUNTRY_RESERVE；KB=KB_XH202612_V50_GOVERNANCE</x:v>
       </x:c>
       <x:c r="I8" s="21" t="str">
-        <x:v>否</x:v>
-      </x:c>
-      <x:c r="J8" s="21" t="str"/>
-      <x:c r="K8" s="21" t="str"/>
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="J8" s="21" t="str">
+        <x:v>证据/B04_20260831/B04_20_AGENT_稳定知识库链路发布_20260901.png</x:v>
+      </x:c>
+      <x:c r="K8" s="21" t="n">
+        <x:v>46265.79597222222</x:v>
+      </x:c>
       <x:c r="L8" s="21" t="str">
-        <x:v>若赛事最终口径不要求独立智能体，登记 N/A 并让 A 确认，不得硬造</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="62" customHeight="1">
+        <x:v>Agent已发布；Prompt版本=V50-B04-LOCAL_FINAL-r10。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="36" hidden="0" customHeight="1">
       <x:c r="A9" s="25" t="str">
         <x:v>测试资源（QA）</x:v>
       </x:c>
@@ -790,21 +802,25 @@
         <x:v>A</x:v>
       </x:c>
       <x:c r="F9" s="21" t="str">
-        <x:v>TEMPLATE_READY / REAL_RUN_0_OF_25</x:v>
+        <x:v>SMOKE_5_OF_5 / AI04_PASS / AI06_PASS / AI22_PASS / AI17_PASS / AI18_PASS / FORMAL_25Q_25_OF_25 / B04_PASS_CANDIDATE_A_REVIEW_PENDING</x:v>
       </x:c>
       <x:c r="G9" s="21" t="str">
-        <x:v>02_25问基准框架 + 06_25问判分记录表</x:v>
+        <x:v>B04_SMOKE_TEST_V50.xlsx；AICHAT_25_RUN_20260901_r1.xlsx；Prompt=V50-B04-LOCAL_FINAL-r10</x:v>
       </x:c>
       <x:c r="H9" s="21" t="str">
-        <x:v>固定模型、KB、AGENT 版本</x:v>
+        <x:v>模型=MDL_XH202612_V50_COUNTRY_RESERVE；KB=KB_XH202612_V50_GOVERNANCE；Agent=AGENT_XH202612_V50_ASSISTANT</x:v>
       </x:c>
       <x:c r="I9" s="21" t="str">
-        <x:v>否</x:v>
-      </x:c>
-      <x:c r="J9" s="21" t="str"/>
-      <x:c r="K9" s="21" t="str"/>
+        <x:v>N/A（记录型资源）</x:v>
+      </x:c>
+      <x:c r="J9" s="21" t="str">
+        <x:v>证据/B04_20260831/B04_18_AI04_正式冒烟_PASS_20260901.png；证据/B04_20260831/B04_19_AI06_正式冒烟_PASS_20260901.png；证据/B04_20260831/QA25_AI06_20260901.png；证据/B04_20260831/B04_21_AI22_正式冒烟_PASS_20260901.png；证据/B04_20260831/QA25_AI22_20260901.png；证据/B04_20260831/B04_22_AI17_正式冒烟_BLOCKED合规_20260901.png；证据/B04_20260831/QA25_AI17_20260901.png；证据/B04_20260831/B04_23_AI18_正式冒烟_PASS_20260901.png；证据/B04_20260831/QA25_AI18_20260901.png；证据/B04_20260831/QA25_AI01_20260901.png；证据/B04_20260831/QA25_AI02_20260901.png；证据/B04_20260831/QA25_AI03_20260901.png；证据/B04_20260831/QA25_AI04_20260901.png；证据/B04_20260831/QA25_AI05_20260901.png；证据/B04_20260831/QA25_AI06_20260901.png；证据/B04_20260831/QA25_AI07_20260901.png；证据/B04_20260831/QA25_AI08_20260901.png；证据/B04_20260831/QA25_AI09_20260901.png；证据/B04_20260831/QA25_AI10_20260901.png；证据/B04_20260831/QA25_AI11_20260901.png；证据/B04_20260831/QA25_AI12_20260901.png；证据/B04_20260831/QA25_AI13_20260901.png；证据/B04_20260831/QA25_AI14_20260901.png；证据/B04_20260831/QA25_AI15_20260901.png；证据/B04_20260831/QA25_AI16_20260901.png；证据/B04_20260831/QA25_AI17_20260901.png；证据/B04_20260831/QA25_AI18_20260901.png；证据/B04_20260831/QA25_AI19_20260901.png；证据/B04_20260831/QA25_AI20_20260901.png；证据/B04_20260831/QA25_AI21_20260901.png；证据/B04_20260831/QA25_AI22_20260901.png；证据/B04_20260831/QA25_AI23_20260901.png；证据/B04_20260831/QA25_AI24_20260901.png；证据/B04_20260831/QA25_AI25_20260901.png</x:v>
+      </x:c>
+      <x:c r="K9" s="21" t="n">
+        <x:v>46265.79597222222</x:v>
+      </x:c>
       <x:c r="L9" s="21" t="str">
-        <x:v>离线基准不是实测；任何修复后 25 题全量回归</x:v>
+        <x:v>冒烟PASS=5/5，复测中=0，未执行=0；正式25问完成=25/25；硬失败=0。</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -819,10 +835,10 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="50" t="str">
-        <x:v>1. 对象未在 SmartBI 实机创建并截图前，“实机存在”填否。
-2. 当前允许配置与 5 题冒烟，但不能写 B04 PASS；正式 25 问仍为 0/25。
-3. A 只读复核和签名只能由 A 本人填写。
-4. 绑定模型只记固定对象名与实际版本证据；不得虚写“最终冻结版已完成”。</x:v>
+        <x:v>1. AIP、KB、Agent 的资源ID、版本和截图必须来自实机。
+2. KB 43条已逐行重存并完成7类7/7检索；旧失败证据继续保留。
+3. 冒烟与25问只按完整原答、source_id、截图和版本判分；修一题必须全25回归。
+4. A只读复核和签名只能由A本人填写；脚本最多写PASS候选，不自动写B04 PASS或最终冻结。</x:v>
       </x:c>
       <x:c r="B12" s="51"/>
       <x:c r="C12" s="51"/>
